--- a/data/nzd0057/nzd0057.xlsx
+++ b/data/nzd0057/nzd0057.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D317"/>
+  <dimension ref="A1:D319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6136,6 +6136,42 @@
         <v>339.44</v>
       </c>
       <c r="D317" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>344.92</v>
+      </c>
+      <c r="C318" t="n">
+        <v>337.23</v>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>344.92</v>
+      </c>
+      <c r="C319" t="n">
+        <v>337.48</v>
+      </c>
+      <c r="D319" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -6152,7 +6188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B369"/>
+  <dimension ref="A1:B371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9845,6 +9881,26 @@
       </c>
       <c r="B369" t="n">
         <v>0.86</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>0.47</v>
       </c>
     </row>
   </sheetData>
@@ -10013,28 +10069,28 @@
         <v>0.1001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05909959434820432</v>
+        <v>0.0518553043587244</v>
       </c>
       <c r="J2" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="K2" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01545147705548866</v>
+        <v>0.01190901276698186</v>
       </c>
       <c r="M2" t="n">
-        <v>2.930615902315269</v>
+        <v>2.944598204310255</v>
       </c>
       <c r="N2" t="n">
-        <v>12.6029930839144</v>
+        <v>12.73373230366977</v>
       </c>
       <c r="O2" t="n">
-        <v>3.550069447759354</v>
+        <v>3.568435554086661</v>
       </c>
       <c r="P2" t="n">
-        <v>349.1689707200727</v>
+        <v>349.2454428202437</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -10091,28 +10147,28 @@
         <v>0.1118</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06060231145251603</v>
+        <v>0.05165247488665296</v>
       </c>
       <c r="J3" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="K3" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01219248188121458</v>
+        <v>0.008844599906033923</v>
       </c>
       <c r="M3" t="n">
-        <v>3.353182552990411</v>
+        <v>3.373102796923518</v>
       </c>
       <c r="N3" t="n">
-        <v>16.84985472392869</v>
+        <v>17.06451671766801</v>
       </c>
       <c r="O3" t="n">
-        <v>4.104857454763648</v>
+        <v>4.130922017863326</v>
       </c>
       <c r="P3" t="n">
-        <v>342.9407389804362</v>
+        <v>343.0352143862511</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -10150,7 +10206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D317"/>
+  <dimension ref="A1:D319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17127,6 +17183,50 @@
         </is>
       </c>
     </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>-35.121748692720224,174.0121027267404</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>-35.12158948007721,174.01298427513603</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>-35.121748692720224,174.0121027267404</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>-35.12158733927474,174.0129834163779</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0057/nzd0057.xlsx
+++ b/data/nzd0057/nzd0057.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D319"/>
+  <dimension ref="A1:D322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6174,6 +6174,60 @@
       <c r="D319" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:00+00:00</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>347.32</v>
+      </c>
+      <c r="C320" t="n">
+        <v>337.11</v>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>348.5</v>
+      </c>
+      <c r="C321" t="n">
+        <v>337.93</v>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:11:29+00:00</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>346.41</v>
+      </c>
+      <c r="C322" t="n">
+        <v>336.56</v>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B371"/>
+  <dimension ref="A1:B374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9901,6 +9955,36 @@
       </c>
       <c r="B371" t="n">
         <v>0.47</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>
@@ -10069,28 +10153,28 @@
         <v>0.1001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0518553043587244</v>
+        <v>0.04599089878695196</v>
       </c>
       <c r="J2" t="n">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="K2" t="n">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01190901276698186</v>
+        <v>0.009510815648299698</v>
       </c>
       <c r="M2" t="n">
-        <v>2.944598204310255</v>
+        <v>2.942939057049518</v>
       </c>
       <c r="N2" t="n">
-        <v>12.73373230366977</v>
+        <v>12.71621952978485</v>
       </c>
       <c r="O2" t="n">
-        <v>3.568435554086661</v>
+        <v>3.565980865033469</v>
       </c>
       <c r="P2" t="n">
-        <v>349.2454428202437</v>
+        <v>349.3074979541901</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -10147,28 +10231,28 @@
         <v>0.1118</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05165247488665296</v>
+        <v>0.03853761252069253</v>
       </c>
       <c r="J3" t="n">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="K3" t="n">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008844599906033923</v>
+        <v>0.004908259734662357</v>
       </c>
       <c r="M3" t="n">
-        <v>3.373102796923518</v>
+        <v>3.402282318468292</v>
       </c>
       <c r="N3" t="n">
-        <v>17.06451671766801</v>
+        <v>17.38150770817271</v>
       </c>
       <c r="O3" t="n">
-        <v>4.130922017863326</v>
+        <v>4.169113539851452</v>
       </c>
       <c r="P3" t="n">
-        <v>343.0352143862511</v>
+        <v>343.17398239813</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -10206,7 +10290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D319"/>
+  <dimension ref="A1:D322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17227,6 +17311,72 @@
         </is>
       </c>
     </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:00+00:00</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>-35.12172814097373,174.01209448279198</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>-35.12159050766238,174.01298468733992</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>-35.12171803636475,174.01209042951888</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>-35.1215834858303,174.01298187061337</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:11:29+00:00</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>-35.121735933511026,174.01209760862193</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>-35.121595217427775,174.01298657660803</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0057/nzd0057.xlsx
+++ b/data/nzd0057/nzd0057.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D322"/>
+  <dimension ref="A1:D323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6228,6 +6228,24 @@
       <c r="D322" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>346.16</v>
+      </c>
+      <c r="C323" t="n">
+        <v>336.76</v>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B374"/>
+  <dimension ref="A1:B375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9985,6 +10003,16 @@
       </c>
       <c r="B374" t="n">
         <v>0.03</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>-0.5</v>
       </c>
     </row>
   </sheetData>
@@ -10153,28 +10181,28 @@
         <v>0.1001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04599089878695196</v>
+        <v>0.04334000831532744</v>
       </c>
       <c r="J2" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K2" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L2" t="n">
-        <v>0.009510815648299698</v>
+        <v>0.008473286001374758</v>
       </c>
       <c r="M2" t="n">
-        <v>2.942939057049518</v>
+        <v>2.945360466550444</v>
       </c>
       <c r="N2" t="n">
-        <v>12.71621952978485</v>
+        <v>12.73602582721519</v>
       </c>
       <c r="O2" t="n">
-        <v>3.565980865033469</v>
+        <v>3.568756902230129</v>
       </c>
       <c r="P2" t="n">
-        <v>349.3074979541901</v>
+        <v>349.3356521275898</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -10231,28 +10259,28 @@
         <v>0.1118</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03853761252069253</v>
+        <v>0.0340347464126055</v>
       </c>
       <c r="J3" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K3" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004908259734662357</v>
+        <v>0.003821043465277341</v>
       </c>
       <c r="M3" t="n">
-        <v>3.402282318468292</v>
+        <v>3.412440976970037</v>
       </c>
       <c r="N3" t="n">
-        <v>17.38150770817271</v>
+        <v>17.49862080388349</v>
       </c>
       <c r="O3" t="n">
-        <v>4.169113539851452</v>
+        <v>4.183135283956699</v>
       </c>
       <c r="P3" t="n">
-        <v>343.17398239813</v>
+        <v>343.2218057520404</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -10290,7 +10318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D322"/>
+  <dimension ref="A1:D323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17377,6 +17405,28 @@
         </is>
       </c>
     </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>-35.121738074317946,174.0120984673665</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>-35.12159350478582,174.01298588960142</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
